--- a/data/trans_bre/P2A_lim_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_lim_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 4,32</t>
+          <t>-2,07; 4,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 6,35</t>
+          <t>-2,26; 6,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 4,22</t>
+          <t>-2,0; 4,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 1,48</t>
+          <t>-6,35; 1,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-37,3; 145,39</t>
+          <t>-37,19; 138,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-28,36; 137,16</t>
+          <t>-26,98; 132,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-38,85; 138,78</t>
+          <t>-33,11; 155,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,73; 14,85</t>
+          <t>-44,96; 14,53</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 3,59</t>
+          <t>-3,2; 3,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 4,57</t>
+          <t>-3,15; 4,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 3,48</t>
+          <t>-3,25; 3,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 3,29</t>
+          <t>-4,11; 3,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,53; 91,73</t>
+          <t>-44,08; 99,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,31; 89,58</t>
+          <t>-34,77; 103,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-49,53; 97,32</t>
+          <t>-47,87; 88,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,79; 46,76</t>
+          <t>-35,23; 48,79</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 9,43</t>
+          <t>-1,08; 8,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 2,99</t>
+          <t>-6,61; 2,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 6,97</t>
+          <t>-4,26; 6,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 14,72</t>
+          <t>-3,25; 16,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 165,7</t>
+          <t>-17,41; 161,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-46,03; 31,96</t>
+          <t>-49,62; 30,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-47,28; 109,07</t>
+          <t>-49,63; 109,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,3; 304,36</t>
+          <t>-20,67; 318,34</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 2,71</t>
+          <t>-2,51; 2,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 4,84</t>
+          <t>-1,31; 4,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 4,19</t>
+          <t>-1,3; 4,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 50,83</t>
+          <t>-3,72; 49,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,34; 37,14</t>
+          <t>-28,81; 39,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 49,37</t>
+          <t>-10,72; 50,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 64,91</t>
+          <t>-15,27; 62,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,63; 344,68</t>
+          <t>-24,55; 379,4</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 4,08</t>
+          <t>-3,97; 4,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 8,68</t>
+          <t>1,71; 8,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 5,62</t>
+          <t>-1,15; 5,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,06; -0,29</t>
+          <t>-10,49; -0,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-32,74; 71,31</t>
+          <t>-36,35; 65,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,8; 123,36</t>
+          <t>14,97; 125,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 81,06</t>
+          <t>-11,0; 80,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-45,84; -1,64</t>
+          <t>-44,53; -2,31</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,58; 6,7</t>
+          <t>0,71; 6,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 6,65</t>
+          <t>-1,38; 6,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 5,91</t>
+          <t>-0,96; 5,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,27; 16,92</t>
+          <t>7,8; 16,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,53; 235,91</t>
+          <t>10,18; 248,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,26; 117,55</t>
+          <t>-13,45; 131,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 131,51</t>
+          <t>-9,9; 135,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69,1; 626,43</t>
+          <t>69,16; 551,06</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,54</t>
+          <t>0,06; 2,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,54</t>
+          <t>0,5; 3,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,0</t>
+          <t>0,31; 3,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 21,33</t>
+          <t>0,19; 22,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 42,02</t>
+          <t>0,38; 46,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,98; 40,31</t>
+          <t>4,98; 40,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,47; 46,35</t>
+          <t>4,06; 46,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 170,35</t>
+          <t>1,55; 201,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_lim_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_lim_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,17</t>
+          <t>-2,08</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-19,04%</t>
+          <t>-18,69%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 4,39</t>
+          <t>-2,41; 4,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 6,45</t>
+          <t>-2,35; 6,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 4,81</t>
+          <t>-1,79; 4,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 1,16</t>
+          <t>-5,48; 1,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-37,19; 138,16</t>
+          <t>-43,33; 124,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-26,98; 132,0</t>
+          <t>-30,66; 143,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-33,11; 155,59</t>
+          <t>-36,66; 138,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-44,96; 14,53</t>
+          <t>-41,52; 13,89</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,19</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-2,05%</t>
+          <t>-1,19%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 3,73</t>
+          <t>-3,13; 3,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 4,88</t>
+          <t>-3,17; 5,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 3,27</t>
+          <t>-3,63; 3,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 3,5</t>
+          <t>-3,85; 3,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,08; 99,1</t>
+          <t>-45,16; 82,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,77; 103,93</t>
+          <t>-36,93; 103,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,87; 88,47</t>
+          <t>-50,48; 81,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,23; 48,79</t>
+          <t>-32,86; 45,13</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,28</t>
+          <t>-0,79</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>-5,17%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 8,85</t>
+          <t>-1,1; 8,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 2,95</t>
+          <t>-6,27; 2,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 6,74</t>
+          <t>-4,14; 6,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 16,33</t>
+          <t>-6,17; 5,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 161,28</t>
+          <t>-16,53; 168,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,62; 30,37</t>
+          <t>-47,97; 30,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-49,63; 109,62</t>
+          <t>-48,92; 102,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-20,67; 318,34</t>
+          <t>-36,09; 39,21</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,58</t>
+          <t>-2,98</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>106,4%</t>
+          <t>-20,2%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 2,75</t>
+          <t>-2,06; 2,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 4,85</t>
+          <t>-1,39; 5,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 4,03</t>
+          <t>-1,26; 3,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 49,35</t>
+          <t>-5,81; 0,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,81; 39,07</t>
+          <t>-23,37; 44,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 50,25</t>
+          <t>-11,54; 53,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 62,26</t>
+          <t>-14,71; 58,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,55; 379,4</t>
+          <t>-35,34; -0,02</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-4,72</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-23,1%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 4,07</t>
+          <t>-4,07; 3,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 8,89</t>
+          <t>1,32; 8,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 5,48</t>
+          <t>-1,13; 5,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,49; -0,38</t>
+          <t>-4,03; 3,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-36,35; 65,77</t>
+          <t>-37,75; 62,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,97; 125,91</t>
+          <t>13,48; 130,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 80,07</t>
+          <t>-11,16; 75,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-44,53; -2,31</t>
+          <t>-19,26; 23,91</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12,77</t>
+          <t>11,24</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>215,64%</t>
+          <t>152,47%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,74</t>
+          <t>0,71; 6,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 6,97</t>
+          <t>-1,32; 6,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 5,78</t>
+          <t>-1,24; 5,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,8; 16,58</t>
+          <t>5,25; 15,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,18; 248,81</t>
+          <t>9,14; 218,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-13,45; 131,86</t>
+          <t>-11,78; 128,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 135,55</t>
+          <t>-13,33; 126,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69,16; 551,06</t>
+          <t>40,98; 396,17</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,99</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,74</t>
+          <t>0,13; 2,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,49</t>
+          <t>0,34; 3,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,06</t>
+          <t>0,28; 3,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 22,87</t>
+          <t>-0,83; 2,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 46,06</t>
+          <t>0,78; 44,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,98; 40,08</t>
+          <t>4,41; 38,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,06; 46,74</t>
+          <t>3,76; 49,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 201,59</t>
+          <t>-5,74; 17,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_lim_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_lim_R-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Población que convive con personas con alguna limitación (física, sensorial o psíquica)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
